--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104514_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104514_W7.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1601</v>
+        <v>4.9203</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1608</v>
+        <v>4.7912</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.1291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9956</v>
+        <v>0.9969</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5758</v>
+        <v>3.5676</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.5802</v>
+        <v>-2.5707</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9677</v>
+        <v>1.9341</v>
       </c>
       <c r="K2" t="n">
-        <v>3.058</v>
+        <v>3.0369</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.972</v>
+        <v>-0.9371</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4898</v>
+        <v>-1.4678</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1906</v>
+        <v>-1.4225</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5898</v>
+        <v>0.0926</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6009</v>
+        <v>-1.5151</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4478</v>
+        <v>4.4353</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.997</v>
+        <v>4.2867</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0054</v>
+        <v>3.3811</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9916</v>
+        <v>0.9056</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9613</v>
+        <v>1.9632</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5583</v>
+        <v>2.559</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5971</v>
+        <v>-0.5958</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0638</v>
+        <v>3.0306</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9151</v>
+        <v>1.8993</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1487</v>
+        <v>1.1313</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1025</v>
+        <v>-1.0674</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7458</v>
+        <v>-1.7271</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0815</v>
+        <v>-0.7872</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3176</v>
+        <v>0.7453</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3991</v>
+        <v>-1.5325</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6987</v>
+        <v>0.7635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1244</v>
+        <v>0.1441</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5642</v>
+        <v>0.4104</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1283</v>
+        <v>0.6634</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6926</v>
+        <v>-0.253</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7708</v>
+        <v>0.2641</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0591</v>
+        <v>0.1896</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7117</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7935</v>
+        <v>0.1463</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1874</v>
+        <v>0.4738</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9808</v>
+        <v>-0.3275</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9285</v>
+        <v>0.1255</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8207</v>
+        <v>0.3553</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8922</v>
+        <v>-0.2298</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4649</v>
+        <v>0.3084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2651</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1998</v>
+        <v>-0.1962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4038</v>
+        <v>1.2615</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6623</v>
+        <v>0.4449</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2585</v>
+        <v>0.8166</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2651</v>
+        <v>0.3977</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1905</v>
+        <v>0.5171</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>-0.1194</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1387</v>
+        <v>0.8638</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4718</v>
+        <v>-0.0722</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1657</v>
+        <v>-1.2506</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.3831</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1657</v>
+        <v>-1.6338</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2598</v>
+        <v>0.2747</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2598</v>
+        <v>-0.1199</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.3946</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2598</v>
+        <v>-3.7785</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2598</v>
+        <v>1.4423</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5.2208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2598</v>
+        <v>-2.3532</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2598</v>
+        <v>0.7682</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.1213</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.4254</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.6741</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-2.0995</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.8569</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.7614</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.1378</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>5.0604</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2593</v>
+        <v>0.2586</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5657</v>
+        <v>0.2586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3064</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4095</v>
+        <v>0.2586</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5181</v>
+        <v>0.2586</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9276</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.2586</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0.2586</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6717</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5354</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2559</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7168</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4483</v>
+        <v>-0.0518</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0722</v>
+        <v>-0.2725</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3761</v>
+        <v>0.2206</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2504</v>
+        <v>-1.5513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.44</v>
+        <v>0.1346</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8104</v>
+        <v>-1.686</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4048</v>
+        <v>-0.7809</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5195</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1147</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8455</v>
+        <v>-0.7704</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0795</v>
+        <v>0.2003</v>
       </c>
       <c r="O8" t="n">
-        <v>0.925</v>
+        <v>-0.9708</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9916</v>
+        <v>0.1533</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0.736</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7829</v>
+        <v>-0.5827</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2534</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6363</v>
+        <v>-0.3645</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0514</v>
+        <v>0.2871</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6877</v>
+        <v>-0.6516</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0414</v>
+        <v>0.0477</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1587</v>
+        <v>0.1607</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.149</v>
+        <v>-0.1419</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9046</v>
+        <v>-0.6399</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>0.0975</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7655</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7079</v>
+        <v>-0.4018</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6887</v>
+        <v>-0.8114</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0192</v>
+        <v>0.4096</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7753</v>
+        <v>0.4153</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4518</v>
+        <v>-0.5143</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.227</v>
+        <v>0.9296</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3155</v>
+        <v>0.6875</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7926</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.1081</v>
+        <v>0.6703</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4597</v>
+        <v>-0.2722</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6592</v>
+        <v>-0.5315</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1189</v>
+        <v>0.2593</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8606</v>
+        <v>0.4819</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7289</v>
+        <v>0.483</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1318</v>
+        <v>-0.0011</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1549</v>
+        <v>-0.6162</v>
       </c>
       <c r="W10" t="n">
-        <v>5.0777</v>
+        <v>-0.6162</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9563</v>
+        <v>-2.2192</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2461</v>
+        <v>-2.238</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2898</v>
+        <v>0.0188</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5536</v>
+        <v>-0.5455</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5539</v>
+        <v>3.5583</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.1075</v>
+        <v>-4.1037</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4184</v>
+        <v>0.3917</v>
       </c>
       <c r="K11" t="n">
-        <v>2.407</v>
+        <v>2.3959</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9886</v>
+        <v>-2.0042</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.972</v>
+        <v>-0.9371</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1469</v>
+        <v>1.1623</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1189</v>
+        <v>-2.0995</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.614</v>
+        <v>-0.8893</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0575</v>
+        <v>0.1019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6715</v>
+        <v>-0.9912</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5178</v>
+        <v>-4.3578</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1279</v>
+        <v>-0.8955</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3899</v>
+        <v>-3.4623</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8385</v>
+        <v>-0.8337</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1846</v>
+        <v>1.1861</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0231</v>
+        <v>-2.0198</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3046</v>
+        <v>0.2963</v>
       </c>
       <c r="K12" t="n">
-        <v>1.091</v>
+        <v>1.0859</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1431</v>
+        <v>-1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4969</v>
+        <v>-0.3542</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1553</v>
+        <v>0.4016</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6584</v>
+        <v>-0.7559</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2689</v>
+        <v>-2.2593</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2689</v>
+        <v>-2.2593</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2719</v>
+        <v>-6.2434</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.3602</v>
+        <v>-5.9032</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0883</v>
+        <v>-0.3402</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0992</v>
+        <v>-1.1029</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6279</v>
+        <v>0.6126</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0164</v>
+        <v>-0.0182</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8028</v>
+        <v>0.7714</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1157</v>
+        <v>-1.0847</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.1245</v>
+        <v>-6.146</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7546</v>
+        <v>-0.714</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7984</v>
+        <v>-0.2837</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0438</v>
+        <v>-0.4303</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0155</v>
+        <v>-1.0121</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5619</v>
+        <v>-1.5568</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.217299999999998</v>
+        <v>-2.826299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4952</v>
+        <v>-0.3986000000000018</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.722</v>
+        <v>-2.4279</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.509</v>
+        <v>-2.4583</v>
       </c>
       <c r="H14" t="n">
-        <v>14.0833</v>
+        <v>14.0738</v>
       </c>
       <c r="I14" t="n">
-        <v>-16.5924</v>
+        <v>-16.5321</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4938</v>
+        <v>4.2979</v>
       </c>
       <c r="K14" t="n">
-        <v>11.185</v>
+        <v>11.064</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.6912</v>
+        <v>-6.7661</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.002800000000001</v>
+        <v>-6.7561</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8985</v>
+        <v>3.0096</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.901199999999999</v>
+        <v>-9.7659</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.4149</v>
+        <v>-20.4868</v>
       </c>
       <c r="R14" t="n">
-        <v>19.2808</v>
+        <v>19.3486</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.5157</v>
+        <v>-6.1539</v>
       </c>
       <c r="T14" t="n">
-        <v>1.603</v>
+        <v>3.0171</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.118900000000002</v>
+        <v>-9.171200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9418</v>
+        <v>6.9238</v>
       </c>
       <c r="W14" t="n">
-        <v>12.823</v>
+        <v>12.773</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.881399999999999</v>
+        <v>-5.849200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0154</v>
+        <v>6.2712</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0358</v>
+        <v>6.4674</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0204</v>
+        <v>-0.1961</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2075</v>
+        <v>2.1907</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1429</v>
+        <v>-1.1376</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3504</v>
+        <v>3.3283</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9386</v>
+        <v>3.8968</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2703</v>
+        <v>3.2385</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7311</v>
+        <v>-1.7061</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3374</v>
+        <v>1.5978</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2975</v>
+        <v>1.7786</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0399</v>
+        <v>-0.1808</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1786</v>
+        <v>3.5253</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8325</v>
+        <v>1.3519</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3461</v>
+        <v>2.1733</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1204</v>
+        <v>0.9281</v>
       </c>
       <c r="H16" t="n">
-        <v>0.57</v>
+        <v>0.1435</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6904</v>
+        <v>0.7846</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6972</v>
+        <v>0.8411</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1531</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4559</v>
+        <v>0.8411</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8176</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5831</v>
+        <v>0.1435</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.0565</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2574</v>
+        <v>0.4575</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5889</v>
+        <v>0.5108</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3315</v>
+        <v>-0.0534</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3032</v>
+        <v>3.3494</v>
       </c>
       <c r="E17" t="n">
-        <v>1.361</v>
+        <v>2.106</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9422</v>
+        <v>1.2434</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9356</v>
+        <v>-0.1299</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1414</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7942</v>
+        <v>-0.6959</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8529</v>
+        <v>0.671</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.1409</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8529</v>
+        <v>-0.4698</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0828</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1414</v>
+        <v>-0.5749</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0586</v>
+        <v>-0.226</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2353</v>
+        <v>1.4306</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5081</v>
+        <v>1.8903</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2728</v>
+        <v>-0.4596</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8801</v>
+        <v>2.449</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9847</v>
+        <v>2.3035</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1046</v>
+        <v>0.1454</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.6216</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9247</v>
+        <v>-1.9352</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3194</v>
+        <v>1.3136</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5182</v>
+        <v>-0.551</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.483</v>
+        <v>-1.5038</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0871</v>
+        <v>-0.0706</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2172</v>
+        <v>0.7943</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7712</v>
+        <v>1.1308</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5541</v>
+        <v>-0.3366</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.767</v>
+        <v>0.7459</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0798</v>
+        <v>0.6736</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6872</v>
+        <v>0.0723</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4467</v>
+        <v>1.7868</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.345</v>
+        <v>-5.8275</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8983</v>
+        <v>7.6143</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5705</v>
+        <v>2.2467</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1039</v>
+        <v>-3.8448</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6744</v>
+        <v>6.0915</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1238</v>
+        <v>-0.4599</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4489</v>
+        <v>-1.9827</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5727</v>
+        <v>1.5228</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2137</v>
+        <v>0.821</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1039</v>
+        <v>0.5454</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1098</v>
+        <v>0.2755</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3423</v>
+        <v>0.3357</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5423</v>
+        <v>-0.749</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>1.0847</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3631</v>
+        <v>-0.4319</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8125</v>
+        <v>-1.3333</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1755</v>
+        <v>0.9014</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1834</v>
+        <v>-0.5745</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1487</v>
+        <v>0.1034</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0346</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1797</v>
+        <v>0.1426</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.4367</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1409</v>
+        <v>1.5793</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8562</v>
+        <v>-0.4553</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8559</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4234</v>
+        <v>0.2808</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4325</v>
+        <v>0.4868</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9058</v>
+        <v>-0.3023</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3412</v>
+        <v>-2.688</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5647</v>
+        <v>2.3856</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8005</v>
+        <v>0.3726</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.8281</v>
+        <v>-0.8073</v>
       </c>
       <c r="I21" t="n">
-        <v>7.6286</v>
+        <v>1.18</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2866</v>
+        <v>0.1707</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.8279</v>
+        <v>0.1411</v>
       </c>
       <c r="L21" t="n">
-        <v>6.1145</v>
+        <v>0.0296</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4861</v>
+        <v>0.2019</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0002</v>
+        <v>-0.9485</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5141</v>
+        <v>1.1504</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-3.8697</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8405</v>
+        <v>0.8988</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5202</v>
+        <v>0.3085</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3203</v>
+        <v>0.5903</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9426</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1401</v>
+        <v>-1.8142</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1975</v>
+        <v>1.1766</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7439</v>
+        <v>0.7385</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1442</v>
+        <v>0.1491</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5997</v>
+        <v>0.5894</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0638</v>
+        <v>0.0487</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M22" t="n">
-        <v>0.68</v>
+        <v>0.6898</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0572</v>
+        <v>0.266</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1059</v>
+        <v>0.4621</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.163</v>
+        <v>-0.1961</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1128</v>
+        <v>-2.1529</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9613</v>
+        <v>-1.9425</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1515</v>
+        <v>-0.2104</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5434</v>
+        <v>-1.5559</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.551</v>
+        <v>-2.5613</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0076</v>
+        <v>1.0054</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6014</v>
+        <v>-0.6367</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4094</v>
+        <v>-0.4351</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.9193</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1416</v>
+        <v>-2.1262</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5913</v>
+        <v>1.5608</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9084</v>
+        <v>0.9705</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6829</v>
+        <v>0.5903</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8938</v>
+        <v>-3.314</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4228</v>
+        <v>-1.2188</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.471</v>
+        <v>-2.0952</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9382</v>
+        <v>0.9378</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7997</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3558</v>
+        <v>1.3387</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4176</v>
+        <v>-0.4009</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9908</v>
+        <v>-0.4112</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4688</v>
+        <v>-0.2325</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.522</v>
+        <v>-0.1786</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7296</v>
+        <v>-4.4698</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1639</v>
+        <v>-2.0622</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5657</v>
+        <v>-2.4076</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7639</v>
+        <v>-1.7568</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4733</v>
+        <v>-1.4679</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2905</v>
+        <v>-0.2889</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6854</v>
+        <v>-0.6953</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1976</v>
+        <v>-0.2036</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4878</v>
+        <v>-0.4917</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0785</v>
+        <v>-1.0615</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6959</v>
+        <v>0.944</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4003</v>
+        <v>1.5257</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7044</v>
+        <v>-0.5816</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.8885</v>
+        <v>-3.8846</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.217399999999998</v>
+        <v>5.7999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.722199999999999</v>
+        <v>2.4277</v>
       </c>
       <c r="F26" t="n">
-        <v>1.495099999999999</v>
+        <v>3.372</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5091</v>
+        <v>2.4584</v>
       </c>
       <c r="H26" t="n">
-        <v>-14.0834</v>
+        <v>-14.0736</v>
       </c>
       <c r="I26" t="n">
-        <v>16.5925</v>
+        <v>16.5321</v>
       </c>
       <c r="J26" t="n">
-        <v>7.002800000000001</v>
+        <v>6.7562</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.8987</v>
+        <v>-3.0095</v>
       </c>
       <c r="L26" t="n">
-        <v>9.901299999999999</v>
+        <v>9.766</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.4937</v>
+        <v>-4.2979</v>
       </c>
       <c r="N26" t="n">
-        <v>-11.1848</v>
+        <v>-11.0642</v>
       </c>
       <c r="O26" t="n">
-        <v>6.691099999999999</v>
+        <v>6.7663</v>
       </c>
       <c r="P26" t="n">
-        <v>1.134199999999999</v>
+        <v>1.138200000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-19.2809</v>
+        <v>-19.3488</v>
       </c>
       <c r="R26" t="n">
-        <v>20.4151</v>
+        <v>20.4868</v>
       </c>
       <c r="S26" t="n">
-        <v>7.515599999999999</v>
+        <v>9.127199999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>9.118600000000001</v>
+        <v>9.171000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.603</v>
+        <v>-0.04379999999999984</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.9416</v>
+        <v>-6.9238</v>
       </c>
       <c r="W26" t="n">
-        <v>5.8814</v>
+        <v>5.8492</v>
       </c>
       <c r="X26" t="n">
-        <v>-12.8229</v>
+        <v>-12.7729</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104514_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104514_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.2593</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.5568</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.849200000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104514_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-12.7729</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
